--- a/balance_generate/input_data/interest_rt.xlsx
+++ b/balance_generate/input_data/interest_rt.xlsx
@@ -1,34 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzimi\Documents\data_engineering\data_projects\git_hub_projects\bank_project\balance_generate\input_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E17B52-3FE8-4FBE-8C8B-34C48DDB75A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3640" yWindow="3640" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>product_code</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>delay</t>
+  </si>
+  <si>
+    <t>index_floor</t>
+  </si>
+  <si>
+    <t>client_floor</t>
+  </si>
+  <si>
+    <t>index_cap</t>
+  </si>
+  <si>
+    <t>client_cap</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +80,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,183 +382,259 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>product_code</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>delay</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>index_floor</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>client_floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>6000</v>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>7060</v>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3">
+        <v>0.75</v>
+      </c>
+      <c r="C3">
         <v>0.5</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>8000</v>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B4">
+        <v>0.6</v>
+      </c>
+      <c r="C4">
+        <v>0.12</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>1000</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>1100</v>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>2000</v>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>2100</v>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>3000</v>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>3100</v>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>4100</v>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="B11">
+        <v>0.8</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>5000</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>7900</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>6300</v>
+      </c>
+      <c r="B14">
+        <v>0.1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/balance_generate/input_data/interest_rt.xlsx
+++ b/balance_generate/input_data/interest_rt.xlsx
@@ -1,67 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzimi\Documents\data_engineering\data_projects\git_hub_projects\bank_project\balance_generate\input_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E17B52-3FE8-4FBE-8C8B-34C48DDB75A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="3640" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3640" yWindow="3640" windowWidth="19200" windowHeight="11170" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>product_code</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>delay</t>
-  </si>
-  <si>
-    <t>index_floor</t>
-  </si>
-  <si>
-    <t>client_floor</t>
-  </si>
-  <si>
-    <t>index_cap</t>
-  </si>
-  <si>
-    <t>client_cap</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -80,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -382,258 +407,295 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>product_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>index_floor</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>client_floor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>index_cap</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>client_cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7060</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>6000</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7900</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6300</v>
+      </c>
+      <c r="B14" t="n">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>7060</v>
-      </c>
-      <c r="B3">
-        <v>0.75</v>
-      </c>
-      <c r="C3">
-        <v>0.5</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>8000</v>
-      </c>
-      <c r="B4">
-        <v>0.6</v>
-      </c>
-      <c r="C4">
-        <v>0.12</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1000</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>1100</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>2000</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>2100</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>3000</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>3100</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>4100</v>
-      </c>
-      <c r="B11">
-        <v>0.8</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>5000</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>7900</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>6300</v>
-      </c>
-      <c r="B14">
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0.1</v>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3200</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/balance_generate/input_data/interest_rt.xlsx
+++ b/balance_generate/input_data/interest_rt.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -433,25 +433,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>delay</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>index_floor</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>client_floor</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>index_cap</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>client_cap</t>
         </is>
@@ -467,13 +462,10 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -487,10 +479,7 @@
       <c r="C3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -504,10 +493,7 @@
       <c r="C4" t="n">
         <v>0.12</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -524,9 +510,6 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,9 +524,6 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -558,9 +538,6 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -575,9 +552,6 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -592,9 +566,6 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -609,9 +580,6 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -626,9 +594,6 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -643,9 +608,6 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -660,9 +622,6 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -671,13 +630,10 @@
       <c r="B14" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -692,9 +648,6 @@
         <v>-0.75</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
         <v>0</v>
       </c>
     </row>
